--- a/downloads/korrigierte_referenz/Projekte_3NF.xlsx
+++ b/downloads/korrigierte_referenz/Projekte_3NF.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER" sheetId="1" r:id="Rc22e5093fbaa4062"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ABTEILUNG" sheetId="2" r:id="R689db53ebc3e4f4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJEKT" sheetId="3" r:id="Rfc8ff2b74b874e94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER_PROJEKT" sheetId="4" r:id="Rc7ee47ca15de405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER" sheetId="1" r:id="R9717a0867a794cab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ABTEILUNG" sheetId="2" r:id="R106382336b6b44a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJEKT" sheetId="3" r:id="Ra1fa1f55be1a4b20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER_PROJEKT" sheetId="4" r:id="Ra783e1964fb04a91"/>
   </x:sheets>
 </x:workbook>
 </file>
